--- a/generate_statistics_graphs/test_lppo_linear_noise_estimator.xlsx
+++ b/generate_statistics_graphs/test_lppo_linear_noise_estimator.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="agent_lppo_13739880_13769003" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="agent_lppo_13739880_13769003"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -170,193 +157,196 @@
     <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) (&lt;&lt; (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) 4)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) (&lt;&lt; (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) 4)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) (&lt;&lt; (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) 4)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) (&lt;&lt; (Vec v1_0 v1_2 v1_1 v1_3 v2_0 v2_2 v2_1 v2_3) 4)) 2)) 1))</t>
   </si>
   <si>
+    <t>dot_product_8</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>dot_product_32</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) ( + ( + ( + ( * v1_8 v2_8 ) ( * v1_9 v2_9 ) ) ( + ( * v1_10 v2_10 ) ( * v1_11 v2_11 ) ) ) ( + ( + ( * v1_12 v2_12 ) ( * v1_13 v2_13 ) ) ( + ( * v1_14 v2_14 ) ( * v1_15 v2_15 ) ) ) ) ) ( + ( + ( + ( + ( * v1_16 v2_16 ) ( * v1_17 v2_17 ) ) ( + ( * v1_18 v2_18 ) ( * v1_19 v2_19 ) ) ) ( + ( + ( * v1_20 v2_20 ) ( * v1_21 v2_21 ) ) ( + ( * v1_22 v2_22 ) ( * v1_23 v2_23 ) ) ) ) ( + ( + ( + ( * v1_24 v2_24 ) ( * v1_25 v2_25 ) ) ( + ( * v1_26 v2_26 ) ( * v1_27 v2_27 ) ) ) ( + ( + ( * v1_28 v2_28 ) ( * v1_29 v2_29 ) ) ( + ( * v1_30 v2_30 ) ( * v1_31 v2_31 ) ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>gx_kernel_4</t>
+  </si>
+  <si>
+    <t>(Vec ( + in_1_1 ( * in_0_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_0_2 2 ) ( * in_0_0 -2 ) ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_0_3 2 ) ( * in_0_1 -2 ) ) ) ( + ( - in_1_2 ) ( * in_0_2 -2 ) ) ( + in_2_1 ( + in_0_1 ( * in_1_1 2 ) ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( + in_0_2 ( - in_0_0 ) ) ( + ( * in_1_2 2 ) ( * in_1_0 -2 ) ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( + in_0_3 ( - in_0_1 ) ) ( + ( * in_1_3 2 ) ( * in_1_1 -2 ) ) ) ) ( + ( - in_2_2 ) ( + ( - in_0_2 ) ( * in_1_2 -2 ) ) ) ( + in_3_1 ( + in_1_1 ( * in_2_1 2 ) ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_2_2 2 ) ( * in_2_0 -2 ) ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_2_3 2 ) ( * in_2_1 -2 ) ) ) ) ( + ( - in_3_2 ) ( + ( - in_1_2 ) ( * in_2_2 -2 ) ) ) ( + in_2_1 ( * in_3_1 2 ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( * in_3_2 2 ) ( * in_3_0 -2 ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( * in_3_3 2 ) ( * in_3_1 -2 ) ) ) ( + ( - in_2_2 ) ( * in_3_2 -2 ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_1 1 1 in_0_2 1 1 1 1 1 1 1 1 in_3_1 1 1 in_3_2) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2))))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_1 1 1 in_0_2 1 1 1 1 1 1 1 1 in_3_1 1 1 in_3_2) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2))))))) 16))</t>
+  </si>
+  <si>
+    <t>matrix_mul_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( * a_0_2 b_2_0 ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( * a_0_2 b_2_1 ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( * a_0_2 b_2_2 ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( * a_1_2 b_2_0 ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( * a_1_2 b_2_1 ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( * a_1_2 b_2_2 ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( * a_2_2 b_2_0 ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( * a_2_2 b_2_1 ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( * a_2_2 b_2_2 ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0 1 1 1 1 1 1 1 1 1) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 0 0 0 0 0 0 0 0 0)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1 1 1 1 1 1 1 1 1 1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0 1 1 1 1 1 1 1 1 1) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 0 0 0 0 0 0 0 0 0)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1 1 1 1 1 1 1 1 1 1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))) 9))</t>
+  </si>
+  <si>
+    <t>max_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>sort_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>tree_50-50_5_1</t>
+  </si>
+  <si>
+    <t>(Vec ( * ( + x9602 x9604 ) ( + ( + x9608 x9610 ) ( + ( * x9613 x9615 ) x9617 ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) (&lt;&lt; (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) (&lt;&lt; (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>tree_100-50_5_1</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>max_5</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( * ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c23 ) ) ( * c23 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c24 ) ) ( * c24 ( + ( * o5 ( - 1 c25 ) ) ( * c25 o2 ) ) ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c13 ) ) ( * c13 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c14 ) ) ( * c14 ( + ( * o5 ( - 1 c15 ) ) ( * c15 o1 ) ) ) ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>box_blur_4</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_3 in_1_2 ) ( + in_1_1 in_0_3 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + in_1_3 in_1_2 ) ( + in_0_3 in_0_2 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_3 ( + in_2_2 in_2_1 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_1_1 in_0_3 ) ( + in_0_2 in_0_1 ) ) ) ( + ( + ( + in_2_3 in_2_2 ) ( + in_1_3 in_1_2 ) ) ( + in_0_3 in_0_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_2 ( + in_3_1 in_3_0 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_2_0 in_1_2 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_3 ( + in_3_2 in_3_1 ) ) ( + in_2_3 in_2_2 ) ) ( + ( + in_2_1 in_1_3 ) ( + in_1_2 in_1_1 ) ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_2 in_3_1 ) ( + in_3_0 in_2_2 ) ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_3_1 in_2_3 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3 in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2 in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))) (&lt;&lt; (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3 in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2 in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))) 16))</t>
+  </si>
+  <si>
+    <t>lin_reg_4</t>
+  </si>
+  <si>
+    <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) 8)) 4))</t>
+  </si>
+  <si>
+    <t>lin_reg_16</t>
+  </si>
+  <si>
+    <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) ( + v2_8 ( + 2 ( * v1_8 5 ) ) ) ( + v2_9 ( + 2 ( * v1_9 5 ) ) ) ( + v2_10 ( + 2 ( * v1_10 5 ) ) ) ( + v2_11 ( + 2 ( * v1_11 5 ) ) ) ( + v2_12 ( + 2 ( * v1_12 5 ) ) ) ( + v2_13 ( + 2 ( * v1_13 5 ) ) ) ( + v2_14 ( + 2 ( * v1_14 5 ) ) ) ( + v2_15 ( + 2 ( * v1_15 5 ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))) (&lt;&lt; (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))) 16))</t>
+  </si>
+  <si>
+    <t>hamming_dist_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecMinus (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) (&lt;&lt; (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) 2)) (&lt;&lt; (VecMinus (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) (&lt;&lt; (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>hamming_dist_5</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>hamming_dist_16</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) ( + ( + ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ( - ( + v1_5 v2_5 ) ( * 2 ( * v1_5 v2_5 ) ) ) ) ( + ( - ( + v1_6 v2_6 ) ( * 2 ( * v1_6 v2_6 ) ) ) ( - ( + v1_7 v2_7 ) ( * 2 ( * v1_7 v2_7 ) ) ) ) ) ) ( + ( + ( + ( - ( + v1_8 v2_8 ) ( * 2 ( * v1_8 v2_8 ) ) ) ( - ( + v1_9 v2_9 ) ( * 2 ( * v1_9 v2_9 ) ) ) ) ( + ( - ( + v1_10 v2_10 ) ( * 2 ( * v1_10 v2_10 ) ) ) ( - ( + v1_11 v2_11 ) ( * 2 ( * v1_11 v2_11 ) ) ) ) ) ( + ( + ( - ( + v1_12 v2_12 ) ( * 2 ( * v1_12 v2_12 ) ) ) ( - ( + v1_13 v2_13 ) ( * 2 ( * v1_13 v2_13 ) ) ) ) ( + ( - ( + v1_14 v2_14 ) ( * 2 ( * v1_14 v2_14 ) ) ) ( - ( + v1_15 v2_15 ) ( * 2 ( * v1_15 v2_15 ) ) ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>poly_reg_4</t>
+  </si>
+  <si>
+    <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) 8)) 4))</t>
+  </si>
+  <si>
+    <t>poly_reg_16</t>
+  </si>
+  <si>
+    <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) ( + c1_4 ( + c2_4 ( * c0_4 ( + c3_4 ( * c0_4 c4_4 ) ) ) ) ) ( + c1_5 ( + c2_5 ( * c0_5 ( + c3_5 ( * c0_5 c4_5 ) ) ) ) ) ( + c1_6 ( + c2_6 ( * c0_6 ( + c3_6 ( * c0_6 c4_6 ) ) ) ) ) ( + c1_7 ( + c2_7 ( * c0_7 ( + c3_7 ( * c0_7 c4_7 ) ) ) ) ) ( + c1_8 ( + c2_8 ( * c0_8 ( + c3_8 ( * c0_8 c4_8 ) ) ) ) ) ( + c1_9 ( + c2_9 ( * c0_9 ( + c3_9 ( * c0_9 c4_9 ) ) ) ) ) ( + c1_10 ( + c2_10 ( * c0_10 ( + c3_10 ( * c0_10 c4_10 ) ) ) ) ) ( + c1_11 ( + c2_11 ( * c0_11 ( + c3_11 ( * c0_11 c4_11 ) ) ) ) ) ( + c1_12 ( + c2_12 ( * c0_12 ( + c3_12 ( * c0_12 c4_12 ) ) ) ) ) ( + c1_13 ( + c2_13 ( * c0_13 ( + c3_13 ( * c0_13 c4_13 ) ) ) ) ) ( + c1_14 ( + c2_14 ( * c0_14 ( + c3_14 ( * c0_14 c4_14 ) ) ) ) ) ( + c1_15 ( + c2_15 ( * c0_15 ( + c3_15 ( * c0_15 c4_15 ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7 c2_8 c2_9 c2_10 c2_11 c2_12 c2_13 c2_14 c2_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7 c3_8 c3_9 c3_10 c3_11 c3_12 c3_13 c3_14 c3_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7 c1_8 c1_9 c1_10 c1_11 c1_12 c1_13 c1_14 c1_15 c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7 c4_8 c4_9 c4_10 c4_11 c4_12 c4_13 c4_14 c4_15))))) (&lt;&lt; (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7 c2_8 c2_9 c2_10 c2_11 c2_12 c2_13 c2_14 c2_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7 c3_8 c3_9 c3_10 c3_11 c3_12 c3_13 c3_14 c3_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7 c1_8 c1_9 c1_10 c1_11 c1_12 c1_13 c1_14 c1_15 c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7 c4_8 c4_9 c4_10 c4_11 c4_12 c4_13 c4_14 c4_15))))) 16))</t>
+  </si>
+  <si>
+    <t>l2_distance_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) 2)) 1))</t>
+  </si>
+  <si>
+    <t>l2_distance_5</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>l2_distance_16</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) ( + ( + ( + ( * ( - c2_8 c1_8 ) ( - c2_8 c1_8 ) ) ( * ( - c2_9 c1_9 ) ( - c2_9 c1_9 ) ) ) ( + ( * ( - c2_10 c1_10 ) ( - c2_10 c1_10 ) ) ( * ( - c2_11 c1_11 ) ( - c2_11 c1_11 ) ) ) ) ( + ( + ( * ( - c2_12 c1_12 ) ( - c2_12 c1_12 ) ) ( * ( - c2_13 c1_13 ) ( - c2_13 c1_13 ) ) ) ( + ( * ( - c2_14 c1_14 ) ( - c2_14 c1_14 ) ) ( * ( - c2_15 c1_15 ) ( - c2_15 c1_15 ) ) ) ) ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) 2)) 1))</t>
+  </si>
+  <si>
+    <t>dot_product_3</t>
+  </si>
+  <si>
+    <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+  </si>
+  <si>
+    <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) 1))</t>
+  </si>
+  <si>
     <t>dot_product_5</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) (&lt;&lt; (VecMul (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) (&lt;&lt; (Vec v1_0 v1_4 v1_2 v1_6 v1_1 v1_5 v1_3 v1_7 v2_0 v2_4 v2_2 v2_6 v2_1 v2_5 v2_3 v2_7) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>dot_product_32</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) ( + ( + ( + ( * v1_8 v2_8 ) ( * v1_9 v2_9 ) ) ( + ( * v1_10 v2_10 ) ( * v1_11 v2_11 ) ) ) ( + ( + ( * v1_12 v2_12 ) ( * v1_13 v2_13 ) ) ( + ( * v1_14 v2_14 ) ( * v1_15 v2_15 ) ) ) ) ) ( + ( + ( + ( + ( * v1_16 v2_16 ) ( * v1_17 v2_17 ) ) ( + ( * v1_18 v2_18 ) ( * v1_19 v2_19 ) ) ) ( + ( + ( * v1_20 v2_20 ) ( * v1_21 v2_21 ) ) ( + ( * v1_22 v2_22 ) ( * v1_23 v2_23 ) ) ) ) ( + ( + ( + ( * v1_24 v2_24 ) ( * v1_25 v2_25 ) ) ( + ( * v1_26 v2_26 ) ( * v1_27 v2_27 ) ) ) ( + ( + ( * v1_28 v2_28 ) ( * v1_29 v2_29 ) ) ( + ( * v1_30 v2_30 ) ( * v1_31 v2_31 ) ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) (&lt;&lt; (VecMul (Vec v1_0 v1_16 v1_8 v1_24 v1_4 v1_20 v1_12 v1_28 v1_2 v1_18 v1_10 v1_26 v1_6 v1_22 v1_14 v1_30 v1_1 v1_17 v1_9 v1_25 v1_5 v1_21 v1_13 v1_29 v1_3 v1_19 v1_11 v1_27 v1_7 v1_23 v1_15 v1_31) (Vec v2_0 v2_16 v2_8 v2_24 v2_4 v2_20 v2_12 v2_28 v2_2 v2_18 v2_10 v2_26 v2_6 v2_22 v2_14 v2_30 v2_1 v2_17 v2_9 v2_25 v2_5 v2_21 v2_13 v2_29 v2_3 v2_19 v2_11 v2_27 v2_7 v2_23 v2_15 v2_31)) 16)) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>gx_kernel_4</t>
-  </si>
-  <si>
-    <t>(Vec ( + in_1_1 ( * in_0_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_0_2 2 ) ( * in_0_0 -2 ) ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_0_3 2 ) ( * in_0_1 -2 ) ) ) ( + ( - in_1_2 ) ( * in_0_2 -2 ) ) ( + in_2_1 ( + in_0_1 ( * in_1_1 2 ) ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( + in_0_2 ( - in_0_0 ) ) ( + ( * in_1_2 2 ) ( * in_1_0 -2 ) ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( + in_0_3 ( - in_0_1 ) ) ( + ( * in_1_3 2 ) ( * in_1_1 -2 ) ) ) ) ( + ( - in_2_2 ) ( + ( - in_0_2 ) ( * in_1_2 -2 ) ) ) ( + in_3_1 ( + in_1_1 ( * in_2_1 2 ) ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_2_2 2 ) ( * in_2_0 -2 ) ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_2_3 2 ) ( * in_2_1 -2 ) ) ) ) ( + ( - in_3_2 ) ( + ( - in_1_2 ) ( * in_2_2 -2 ) ) ) ( + in_2_1 ( * in_3_1 2 ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( * in_3_2 2 ) ( * in_3_0 -2 ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( * in_3_3 2 ) ( * in_3_1 -2 ) ) ) ( + ( - in_2_2 ) ( * in_3_2 -2 ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_1 1 1 in_0_2 1 1 1 1 1 1 1 1 in_3_1 1 1 in_3_2) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2))))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_1 1 1 in_0_2 1 1 1 1 1 1 1 1 in_3_1 1 1 in_3_2) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2))))))) 16))</t>
-  </si>
-  <si>
-    <t>matrix_mul_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( * a_0_2 b_2_0 ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( * a_0_2 b_2_1 ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( * a_0_2 b_2_2 ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( * a_1_2 b_2_0 ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( * a_1_2 b_2_1 ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( * a_1_2 b_2_2 ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( * a_2_2 b_2_0 ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( * a_2_2 b_2_1 ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( * a_2_2 b_2_2 ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0 1 1 1 1 1 1 1 1 1) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 0 0 0 0 0 0 0 0 0)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1 1 1 1 1 1 1 1 1 1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0 1 1 1 1 1 1 1 1 1) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 0 0 0 0 0 0 0 0 0)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1 1 1 1 1 1 1 1 1 1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))) 9))</t>
-  </si>
-  <si>
-    <t>max_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) (&lt;&lt; (VecMul (Vec o3 1 1 o3 c23 1 1 c13) (VecMinus (Vec 1 c12 1 1 o2 0 0 o1) (Vec c23 0 c12 c13 0 0 0 0))) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>sort_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 1 (- 1 c23) c13 1 1 c23) (VecMinus (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) (&lt;&lt; (VecAdd (Vec 0 0 0 (* o312 (- 1 c13)) 0 0 0 0 0 0 0 0 0 0 0 0) (Vec 1 c12 1 (* c13 o132) o213 0 0 o123 c13 0 c12 0 0 0 0 0)) 8))) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>tree_50-50_5_1</t>
-  </si>
-  <si>
-    <t>(Vec ( * ( + x9602 x9604 ) ( + ( + x9608 x9610 ) ( + ( * x9613 x9615 ) x9617 ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) (&lt;&lt; (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) (&lt;&lt; (VecAdd (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) (&lt;&lt; (Vec x9602 x9608 x9604 (* x9613 x9615) 0 x9610 0 x9617) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>tree_100-50_5_1</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) (&lt;&lt; (VecMul (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) (&lt;&lt; (VecMul (Vec 1 1 x9619 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 x9622 1 1 1 x9629 1 1 1 1 1 1 1 1 1) (VecAdd (VecMul (Vec 1 x9634 1 1 1 1 1 1 1 x9641 1 1 1 x9656 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 x9635 0 0 x9611 x9649 x9626 0 x9607 x9642 0 0 x9614 x9657 0 0 0 0 0 0 0 x9652 0 0 0 0 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 x9644 1 1 1 x9659 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec x9604 (+ x9637 x9638) x9620 0 x9612 x9650 x9627 1 x9608 x9645 0 0 x9615 x9660 0 0 x9605 1 x9623 1 1 x9653 x9630 1 1 1 1 1 1 1 1 1)))) 16)) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>max_5</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( * ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c23 ) ) ( * c23 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c24 ) ) ( * c24 ( + ( * o5 ( - 1 c25 ) ) ( * c25 o2 ) ) ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c13 ) ) ( * c13 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c14 ) ) ( * c14 ( + ( * o5 ( - 1 c15 ) ) ( * c15 o1 ) ) ) ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) 2)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (VecMinus (Vec 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c45 0 0 c45 0 0 0 0 0 0 0 0 c45 0 0 c45 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))) (VecMul (Vec c45 1 1 c45 1 1 1 1 1 1 1 1 c45 1 1 c45 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec o4 1 1 o4 1 1 1 1 1 1 1 1 o4 1 1 o4 c34 1 1 c34 1 1 1 1 1 1 1 1 c24 1 1 c14))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 o5 1 1 o5 1 1 1 1 1 1 1 1 o5 1 1 o5) (VecMinus (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 1 0 0 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c35 0 0 c35 0 0 0 0 0 0 0 0 c25 0 0 c15))) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c35 1 1 c35 1 1 1 1 1 1 1 1 c25 1 1 c15) (VecMinus (Vec 1 c12 1 1 c23 0 0 c13 1 1 1 1 1 1 1 1 o3 0 0 o3 0 0 0 0 0 0 0 0 o2 0 0 o1) (Vec c34 0 c12 c34 0 0 0 0 c23 0 0 c13 c24 0 0 c14 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0))))) 16)) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>box_blur_4</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_3 in_1_2 ) ( + in_1_1 in_0_3 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + in_1_3 in_1_2 ) ( + in_0_3 in_0_2 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_3 ( + in_2_2 in_2_1 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_1_1 in_0_3 ) ( + in_0_2 in_0_1 ) ) ) ( + ( + ( + in_2_3 in_2_2 ) ( + in_1_3 in_1_2 ) ) ( + in_0_3 in_0_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_2 ( + in_3_1 in_3_0 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_2_0 in_1_2 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_3 ( + in_3_2 in_3_1 ) ) ( + in_2_3 in_2_2 ) ) ( + ( + in_2_1 in_1_3 ) ( + in_1_2 in_1_1 ) ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_2 in_3_1 ) ( + in_3_0 in_2_2 ) ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_3_1 in_2_3 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3 in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2 in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))) (&lt;&lt; (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3 in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2 in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))) 16))</t>
-  </si>
-  <si>
-    <t>lin_reg_4</t>
-  </si>
-  <si>
-    <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3) (Vec v2_0 v2_1 v2_2 v2_3 2 2 2 2 0 0 0 0 5 5 5 5)) 8)) 4))</t>
-  </si>
-  <si>
-    <t>lin_reg_16</t>
-  </si>
-  <si>
-    <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) ( + v2_8 ( + 2 ( * v1_8 5 ) ) ) ( + v2_9 ( + 2 ( * v1_9 5 ) ) ) ( + v2_10 ( + 2 ( * v1_10 5 ) ) ) ( + v2_11 ( + 2 ( * v1_11 5 ) ) ) ( + v2_12 ( + 2 ( * v1_12 5 ) ) ) ( + v2_13 ( + 2 ( * v1_13 5 ) ) ) ( + v2_14 ( + 2 ( * v1_14 5 ) ) ) ( + v2_15 ( + 2 ( * v1_15 5 ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))) (&lt;&lt; (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))) 16))</t>
-  </si>
-  <si>
-    <t>hamming_dist_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecMinus (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) (&lt;&lt; (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) 2)) (&lt;&lt; (VecMinus (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) (&lt;&lt; (VecAdd (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) (&lt;&lt; (VecMinus (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) (&lt;&lt; (VecMul (Vec 1 1 1 2 1 1 1 1 (* v1_0 v2_0) 1 1 1 2 1 1 1) (VecMul (Vec 1 1 1 v1_2 1 1 1 1 1 1 1 1 v1_1 1 1 1) (VecAdd (Vec v1_0 0 0 0 v1_1 0 0 0 0 0 0 0 0 0 0 0) (Vec v2_0 v1_2 0 v2_2 v2_1 v2_2 0 0 2 0 0 0 v2_1 0 0 0)))) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>hamming_dist_5</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) (&lt;&lt; (VecMul (Vec 1 1 1 1 (* v1_0 v2_0) 1 2 2 1 1 1 1 1 1 1 1) (VecMul (Vec 1 1 1 1 1 1 v1_1 v1_4 1 1 1 1 1 1 1 1) (VecMinus (VecAdd (Vec 0 v1_2 0 0 0 0 0 0 0 v1_3 0 0 0 0 0 0) (Vec v1_0 v2_2 v1_1 v1_4 2 0 v2_1 v2_4 v2_0 v2_3 v2_1 v2_4 0 0 0 0)) (VecMul (Vec 1 2 1 1 1 1 1 1 1 2 1 1 1 1 1 1) (VecMul (Vec 1 v1_2 1 1 1 1 1 1 1 v1_3 1 1 1 1 1 1) (Vec 0 v2_2 0 0 0 0 0 0 0 v2_3 0 0 0 0 0 0)))))) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>hamming_dist_16</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) ( + ( + ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ( - ( + v1_5 v2_5 ) ( * 2 ( * v1_5 v2_5 ) ) ) ) ( + ( - ( + v1_6 v2_6 ) ( * 2 ( * v1_6 v2_6 ) ) ) ( - ( + v1_7 v2_7 ) ( * 2 ( * v1_7 v2_7 ) ) ) ) ) ) ( + ( + ( + ( - ( + v1_8 v2_8 ) ( * 2 ( * v1_8 v2_8 ) ) ) ( - ( + v1_9 v2_9 ) ( * 2 ( * v1_9 v2_9 ) ) ) ) ( + ( - ( + v1_10 v2_10 ) ( * 2 ( * v1_10 v2_10 ) ) ) ( - ( + v1_11 v2_11 ) ( * 2 ( * v1_11 v2_11 ) ) ) ) ) ( + ( + ( - ( + v1_12 v2_12 ) ( * 2 ( * v1_12 v2_12 ) ) ) ( - ( + v1_13 v2_13 ) ( * 2 ( * v1_13 v2_13 ) ) ) ) ( + ( - ( + v1_14 v2_14 ) ( * 2 ( * v1_14 v2_14 ) ) ) ( - ( + v1_15 v2_15 ) ( * 2 ( * v1_15 v2_15 ) ) ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) (&lt;&lt; (Vec v1_0 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15 v2_0 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15) 16)) (VecMul (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) (&lt;&lt; (VecMul (Vec v1_0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 v1_8 v1_4 v1_12 v1_2 v1_10 v1_6 v1_14 v1_1 v1_9 v1_5 v1_13 v1_3 v1_11 v1_7 v1_15) (Vec v2_0 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 v2_8 v2_4 v2_12 v2_2 v2_10 v2_6 v2_14 v2_1 v2_9 v2_5 v2_13 v2_3 v2_11 v2_7 v2_15)) 16))) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>poly_reg_4</t>
-  </si>
-  <si>
-    <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) 8)) (&lt;&lt; (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) (&lt;&lt; (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3) (Vec c1_0 c1_1 c1_2 c1_3 c2_0 c2_1 c2_2 c2_3 0 0 0 0 c4_0 c4_1 c4_2 c4_3)))) 8)) 4))</t>
-  </si>
-  <si>
-    <t>poly_reg_16</t>
-  </si>
-  <si>
-    <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) ( + c1_4 ( + c2_4 ( * c0_4 ( + c3_4 ( * c0_4 c4_4 ) ) ) ) ) ( + c1_5 ( + c2_5 ( * c0_5 ( + c3_5 ( * c0_5 c4_5 ) ) ) ) ) ( + c1_6 ( + c2_6 ( * c0_6 ( + c3_6 ( * c0_6 c4_6 ) ) ) ) ) ( + c1_7 ( + c2_7 ( * c0_7 ( + c3_7 ( * c0_7 c4_7 ) ) ) ) ) ( + c1_8 ( + c2_8 ( * c0_8 ( + c3_8 ( * c0_8 c4_8 ) ) ) ) ) ( + c1_9 ( + c2_9 ( * c0_9 ( + c3_9 ( * c0_9 c4_9 ) ) ) ) ) ( + c1_10 ( + c2_10 ( * c0_10 ( + c3_10 ( * c0_10 c4_10 ) ) ) ) ) ( + c1_11 ( + c2_11 ( * c0_11 ( + c3_11 ( * c0_11 c4_11 ) ) ) ) ) ( + c1_12 ( + c2_12 ( * c0_12 ( + c3_12 ( * c0_12 c4_12 ) ) ) ) ) ( + c1_13 ( + c2_13 ( * c0_13 ( + c3_13 ( * c0_13 c4_13 ) ) ) ) ) ( + c1_14 ( + c2_14 ( * c0_14 ( + c3_14 ( * c0_14 c4_14 ) ) ) ) ) ( + c1_15 ( + c2_15 ( * c0_15 ( + c3_15 ( * c0_15 c4_15 ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7 c2_8 c2_9 c2_10 c2_11 c2_12 c2_13 c2_14 c2_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7 c3_8 c3_9 c3_10 c3_11 c3_12 c3_13 c3_14 c3_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7 c1_8 c1_9 c1_10 c1_11 c1_12 c1_13 c1_14 c1_15 c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7 c4_8 c4_9 c4_10 c4_11 c4_12 c4_13 c4_14 c4_15))))) (&lt;&lt; (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7 c2_8 c2_9 c2_10 c2_11 c2_12 c2_13 c2_14 c2_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (VecAdd (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7 c3_8 c3_9 c3_10 c3_11 c3_12 c3_13 c3_14 c3_15) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7 c0_8 c0_9 c0_10 c0_11 c0_12 c0_13 c0_14 c0_15) (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7 c1_8 c1_9 c1_10 c1_11 c1_12 c1_13 c1_14 c1_15 c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7 c4_8 c4_9 c4_10 c4_11 c4_12 c4_13 c4_14 c4_15))))) 16))</t>
-  </si>
-  <si>
-    <t>l2_distance_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) (&lt;&lt; (Vec c2_0 c2_2 c2_1 0 c1_0 c1_2 c1_1 0) 4))) 2)) 1))</t>
-  </si>
-  <si>
-    <t>l2_distance_5</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) (&lt;&lt; (VecMinus (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) (&lt;&lt; (VecAdd (Vec 0 (* (- c2_2 c1_2) (- c2_2 c1_2)) 0 0 0 0 0 0 0 0 0 0 0 0 0 0) (Vec c2_0 (* (- c2_3 c1_3) (- c2_3 c1_3)) c2_1 c2_4 c2_0 1 c2_1 c2_4 c1_0 0 c1_1 c1_4 c1_0 0 c1_1 c1_4)) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>l2_distance_16</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) ( + ( + ( + ( * ( - c2_8 c1_8 ) ( - c2_8 c1_8 ) ) ( * ( - c2_9 c1_9 ) ( - c2_9 c1_9 ) ) ) ( + ( * ( - c2_10 c1_10 ) ( - c2_10 c1_10 ) ) ( * ( - c2_11 c1_11 ) ( - c2_11 c1_11 ) ) ) ) ( + ( + ( * ( - c2_12 c1_12 ) ( - c2_12 c1_12 ) ) ( * ( - c2_13 c1_13 ) ( - c2_13 c1_13 ) ) ) ( + ( * ( - c2_14 c1_14 ) ( - c2_14 c1_14 ) ) ( * ( - c2_15 c1_15 ) ( - c2_15 c1_15 ) ) ) ) ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) (&lt;&lt; (VecMinus (Vec c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15 c2_0 c2_8 c2_4 c2_12 c2_2 c2_10 c2_6 c2_14 c2_1 c2_9 c2_5 c2_13 c2_3 c2_11 c2_7 c2_15) (Vec c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15 c1_0 c1_8 c1_4 c1_12 c1_2 c1_10 c1_6 c1_14 c1_1 c1_9 c1_5 c1_13 c1_3 c1_11 c1_7 c1_15)) 16)) 8)) 4)) 2)) 1))</t>
-  </si>
-  <si>
-    <t>dot_product_3</t>
-  </si>
-  <si>
-    <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
-  </si>
-  <si>
-    <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) 1))</t>
   </si>
   <si>
     <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ( * v1_4 v2_4 ) ) ) )</t>
@@ -440,381 +430,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -838,331 +486,54 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1173,10 +544,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1214,71 +585,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1306,7 +677,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1329,11 +700,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1342,13 +713,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1358,7 +729,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1367,7 +738,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1376,7 +747,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1384,10 +755,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1447,51 +818,55 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="94.7238095238095" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5809523809524" style="1" customWidth="1"/>
-    <col min="4" max="6" width="13.5809523809524" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.5809523809524" style="3" customWidth="1"/>
+    <col min="1" max="1" style="7" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="94.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1501,23 +876,23 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>10006</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>320</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>5</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="6">
         <v>7.18793188333007</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="6">
         <v>8.38592053055175</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1527,23 +902,23 @@
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>36006</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>15</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>10</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="6">
         <v>7.18793188333007</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="6">
         <v>8.38592053055175</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1553,23 +928,23 @@
       <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>6006</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>250</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>4</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6">
         <v>41.7688839551546</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1579,23 +954,23 @@
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>24006</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>108</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>4</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="6">
         <v>39.3729066607112</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1605,23 +980,23 @@
       <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>4759</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>453</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>7</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>78.7458133214225</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,23 +1006,23 @@
       <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>9760</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>618</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>8</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>76.3498360269791</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="6">
         <v>81.1417906158658</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -1657,23 +1032,23 @@
       <c r="C8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>39762</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>1065</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>10</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>78.7458133214225</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>84.7357565575308</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -1683,23 +1058,23 @@
       <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>10009</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>354</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>6</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <v>77.5478246742008</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1709,23 +1084,23 @@
       <c r="C10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>40009</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>212</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>6</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <v>75.1518473797574</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -1735,23 +1110,23 @@
       <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>3757</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>284</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>44.1648612495979</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -1761,23 +1136,23 @@
       <c r="C12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>7758</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>401</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>6</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="6">
         <v>41.7688839551546</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="6">
         <v>46.5608385440413</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -1787,23 +1162,23 @@
       <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>31760</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>713</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>9</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="6">
         <v>44.1648612495979</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="6">
         <v>50.1548044857063</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -1813,23 +1188,23 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>1756</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>282</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>4</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="6">
         <v>42.9668726023763</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
@@ -1839,23 +1214,23 @@
       <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>3757</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>399</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="6">
         <v>45.3628498968196</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -1865,23 +1240,23 @@
       <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>15759</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>710</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>7</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="6">
         <v>42.9668726023763</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <v>48.9568158384847</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
@@ -1891,23 +1266,23 @@
       <c r="C17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>21507</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>2084</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>11</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="6">
         <v>114.184500834579</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -1917,23 +1292,23 @@
       <c r="C18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>11256</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>370</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <v>6</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <v>75.1518473797574</v>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>59</v>
       </c>
@@ -1943,23 +1318,23 @@
       <c r="C19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>3009</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>386</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <v>6</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>78.7458133214225</v>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
         <v>62</v>
       </c>
@@ -1969,23 +1344,23 @@
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>5012</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>2506</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <v>8</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="6">
         <v>110.930788098804</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="6">
         <v>116.920731334912</v>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
         <v>65</v>
       </c>
@@ -1995,23 +1370,23 @@
       <c r="C21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>1508</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>534</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="5">
         <v>4</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="6">
         <v>73.9538587325357</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="6">
         <v>77.5478246742008</v>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
         <v>68</v>
       </c>
@@ -2021,23 +1396,23 @@
       <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="5">
         <v>7760</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="5">
         <v>1365</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="5">
         <v>10</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <v>108.53481080436</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="6">
         <v>152.699672053958</v>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
         <v>71</v>
       </c>
@@ -2047,23 +1422,23 @@
       <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <v>15015</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>1319</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="5">
         <v>16</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="6">
         <v>146.70972881785</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="6">
         <v>152.699672053958</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
         <v>74</v>
       </c>
@@ -2073,23 +1448,23 @@
       <c r="C24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="5">
         <v>21006</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>78</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="5">
         <v>6</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="6">
         <v>7.18793188333007</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="6">
         <v>8.38592053055175</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -2099,23 +1474,23 @@
       <c r="C25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <v>3006</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>230</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="5">
         <v>4</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <v>41.7688839551546</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
         <v>80</v>
       </c>
@@ -2125,23 +1500,23 @@
       <c r="C26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <v>12006</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>175</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="5">
         <v>4</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="6">
         <v>40.5708953079329</v>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
         <v>83</v>
       </c>
@@ -2151,23 +1526,23 @@
       <c r="C27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <v>3509</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="5">
         <v>755</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="5">
         <v>8</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="6">
         <v>82.3397792630875</v>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="1" t="s">
         <v>86</v>
       </c>
@@ -2177,23 +1552,23 @@
       <c r="C28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="5">
         <v>6010</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="5">
         <v>960</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="5">
         <v>11</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="6">
         <v>76.3498360269791</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="6">
         <v>151.501683406737</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
@@ -2203,23 +1578,23 @@
       <c r="C29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="5">
         <v>19761</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="5">
         <v>1119</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="5">
         <v>9</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>77.5478246742008</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="6">
         <v>83.5377679103092</v>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1" t="s">
         <v>92</v>
       </c>
@@ -2229,23 +1604,23 @@
       <c r="C30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>5009</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="5">
         <v>334</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="5">
         <v>6</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="6">
         <v>77.5478246742008</v>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="1" t="s">
         <v>95</v>
       </c>
@@ -2255,23 +1630,23 @@
       <c r="C31" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <v>20009</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="5">
         <v>279</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="5">
         <v>6</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="6">
         <v>75.1518473797574</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="6">
         <v>76.3498360269791</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="1" t="s">
         <v>98</v>
       </c>
@@ -2281,23 +1656,23 @@
       <c r="C32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <v>2757</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="5">
         <v>285</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="5">
         <v>6</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="6">
         <v>44.1648612495979</v>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="1" t="s">
         <v>101</v>
       </c>
@@ -2307,23 +1682,23 @@
       <c r="C33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>4758</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>1904</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="5">
         <v>7</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="6">
         <v>41.7688839551546</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="6">
         <v>82.3397792630875</v>
       </c>
     </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="1" t="s">
         <v>104</v>
       </c>
@@ -2333,23 +1708,23 @@
       <c r="C34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <v>15759</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>710</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="5">
         <v>7</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="6">
         <v>42.9668726023763</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="6">
         <v>48.9568158384847</v>
       </c>
     </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="1" t="s">
         <v>107</v>
       </c>
@@ -2359,258 +1734,257 @@
       <c r="C35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="5">
         <v>1256</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>215</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="5">
         <v>4</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="6">
         <v>41.7688839551546</v>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="7">
+        <v>112</v>
+      </c>
+      <c r="D36" s="5">
         <v>2257</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>1035</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="5">
         <v>4</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="6">
         <v>78.7458133214225</v>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="7">
+        <v>115</v>
+      </c>
+      <c r="D37" s="5">
         <v>7758</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>708</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="5">
         <v>6</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="6">
         <v>41.7688839551546</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="6">
         <v>47.758827191263</v>
       </c>
     </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="7">
+        <v>118</v>
+      </c>
+      <c r="D38" s="5">
         <v>9757</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="5">
         <v>1875</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="5">
         <v>7</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="6">
         <v>114.184500834579</v>
       </c>
     </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="7">
+        <v>121</v>
+      </c>
+      <c r="D39" s="5">
         <v>37757</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>518</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="5">
         <v>13</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="6">
         <v>40.5708953079329</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="6">
         <v>111.788523540136</v>
       </c>
     </row>
-    <row r="40" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="7">
+        <v>124</v>
+      </c>
+      <c r="D40" s="5">
         <v>28006</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="5">
         <v>275</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="5">
         <v>5</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="6">
         <v>39.3729066607112</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="6">
         <v>40.5708953079329</v>
       </c>
     </row>
-    <row r="41" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="7">
+        <v>127</v>
+      </c>
+      <c r="D41" s="5">
         <v>7012</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="5">
         <v>912</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="5">
         <v>8</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="6">
         <v>110.930788098804</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="6">
         <v>116.920731334912</v>
       </c>
     </row>
-    <row r="42" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" s="7">
+        <v>130</v>
+      </c>
+      <c r="D42" s="5">
         <v>29021</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="5">
         <v>16173</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="5">
         <v>15</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="6">
         <v>218.267610255942</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="6">
         <v>224.257553492051</v>
       </c>
     </row>
-    <row r="43" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="7">
+        <v>133</v>
+      </c>
+      <c r="D43" s="5">
         <v>8018</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="5">
         <v>6270</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="5">
         <v>9</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="6">
         <v>182.488669536896</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="6">
         <v>256.442528269432</v>
       </c>
     </row>
-    <row r="44" ht="18.75" customHeight="1" spans="1:8">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="7">
+        <v>136</v>
+      </c>
+      <c r="D44" s="5">
         <v>7761</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="5">
         <v>1008</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="5">
         <v>6</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="6">
         <v>141.917774228963</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="6">
         <v>147.907717465071</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>